--- a/streamlit_wec_full_app_repo/bluechoice_data.xlsx
+++ b/streamlit_wec_full_app_repo/bluechoice_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4660" yWindow="620" windowWidth="40140" windowHeight="22780" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Themes Tab" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,13 +23,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -55,12 +61,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -103,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -115,6 +136,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3482,7 +3506,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7036907056248767</v>
+        <v>0.6444811743331381</v>
       </c>
     </row>
     <row r="3">
@@ -3495,7 +3519,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4116939958970541</v>
+        <v>0.4419563242340971</v>
       </c>
     </row>
     <row r="4">
@@ -3508,7 +3532,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.2991383665669847</v>
+        <v>0.4057682653851535</v>
       </c>
     </row>
   </sheetData>
@@ -3522,10 +3546,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="34.33203125" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="88.83203125" customWidth="1" min="6" max="6"/>
+    <col width="69.83203125" customWidth="1" min="7" max="7"/>
+    <col width="52.6640625" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4083,12 +4110,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4102,27 +4129,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.2</v>
       </c>
-      <c r="G17" t="n">
-        <v>3</v>
-      </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4136,27 +4163,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4173,24 +4200,24 @@
         <v>4</v>
       </c>
       <c r="F19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.2</v>
       </c>
-      <c r="G19" t="n">
-        <v>3</v>
-      </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4207,24 +4234,24 @@
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="G20" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4244,21 +4271,21 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4278,21 +4305,21 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4309,24 +4336,24 @@
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1428571428571428</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4343,10 +4370,10 @@
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="H24" t="n">
         <v>0.2</v>
@@ -4355,12 +4382,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4374,27 +4401,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4408,27 +4435,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4442,7 +4469,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
@@ -4457,12 +4484,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4476,27 +4503,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4510,27 +4537,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4544,27 +4571,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3333333333333333</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
         <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-07-29 16:28:05</t>
+          <t>2025-08-06 17:38:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cate</t>
+          <t>Bill Staby</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4578,7 +4605,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
         <v>0.2</v>
@@ -4593,12 +4620,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4615,24 +4642,24 @@
         <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4652,21 +4679,21 @@
         <v>3</v>
       </c>
       <c r="G33" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H33" t="n">
         <v>0.2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4680,27 +4707,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4714,27 +4741,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4748,7 +4775,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>1</v>
@@ -4763,12 +4790,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4782,27 +4809,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4816,7 +4843,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
@@ -4831,12 +4858,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4850,27 +4877,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4884,7 +4911,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -4899,12 +4926,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4918,7 +4945,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>1</v>
@@ -4933,12 +4960,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4952,7 +4979,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -4967,12 +4994,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4986,27 +5013,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5020,27 +5047,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5054,27 +5081,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-08-06 17:38:56</t>
+          <t>2025-08-07 12:34:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bill Staby</t>
+          <t>Jeff Scruggs</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5088,27 +5115,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0.2</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5125,24 +5152,24 @@
         <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1428571428571428</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5159,24 +5186,24 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5190,27 +5217,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5224,27 +5251,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5258,27 +5285,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5292,13 +5319,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
         <v>0.3333333333333333</v>
@@ -5307,12 +5334,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5326,27 +5353,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5360,27 +5387,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5394,7 +5421,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -5409,12 +5436,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5428,7 +5455,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
@@ -5443,12 +5470,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5462,7 +5489,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -5477,12 +5504,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5496,27 +5523,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5530,7 +5557,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
@@ -5545,12 +5572,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5564,27 +5591,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-08-07 12:34:54</t>
+          <t>2025-08-11 13:29:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jeff Scruggs</t>
+          <t>Danesh Tafti</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5598,27 +5625,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5632,27 +5659,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="G62" t="n">
         <v>3</v>
       </c>
       <c r="H62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5666,7 +5693,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -5681,12 +5708,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5706,21 +5733,21 @@
         <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5737,24 +5764,24 @@
         <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5771,24 +5798,24 @@
         <v>3</v>
       </c>
       <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5808,7 +5835,7 @@
         <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0.3333333333333333</v>
@@ -5817,12 +5844,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5836,27 +5863,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5870,27 +5897,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5904,7 +5931,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -5919,12 +5946,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5938,27 +5965,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5972,7 +5999,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
@@ -5987,12 +6014,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6006,13 +6033,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H73" t="n">
         <v>1</v>
@@ -6021,12 +6048,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6040,27 +6067,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6077,24 +6104,24 @@
         <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-08-11 13:29:47</t>
+          <t>2025-08-21 13:24:27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Danesh Tafti</t>
+          <t>Eric Wade</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6111,24 +6138,24 @@
         <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6142,13 +6169,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
@@ -6157,12 +6184,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6176,13 +6203,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
@@ -6191,12 +6218,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6210,27 +6237,27 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F79" t="n">
         <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6244,27 +6271,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6278,27 +6305,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6312,27 +6339,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6346,27 +6373,27 @@
         </is>
       </c>
       <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" t="n">
         <v>5</v>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6380,13 +6407,13 @@
         </is>
       </c>
       <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="n">
         <v>5</v>
       </c>
-      <c r="F84" t="n">
-        <v>3</v>
-      </c>
       <c r="G84" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
         <v>0.1428571428571428</v>
@@ -6395,12 +6422,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6414,7 +6441,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -6429,12 +6456,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6448,27 +6475,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6482,7 +6509,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -6497,12 +6524,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6516,13 +6543,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>1</v>
@@ -6531,12 +6558,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6550,27 +6577,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6584,27 +6611,27 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H90" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-08-21 13:24:27</t>
+          <t>2025-08-22 15:18:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Eric Wade</t>
+          <t>Lindsay Dubbs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6618,27 +6645,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6652,27 +6679,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6686,13 +6713,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
@@ -6701,12 +6728,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6720,27 +6747,27 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6754,27 +6781,27 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6788,27 +6815,27 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6822,27 +6849,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6856,27 +6883,27 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6890,27 +6917,27 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1428571428571428</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6927,24 +6954,24 @@
         <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6973,12 +7000,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7007,12 +7034,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7029,24 +7056,24 @@
         <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7063,24 +7090,24 @@
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7094,13 +7121,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>1</v>
@@ -7109,12 +7136,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2025-08-22 15:18:30</t>
+          <t>2026-01-12 19:36:55</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lindsay Dubbs</t>
+          <t>Lisheng Yang</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7128,16 +7155,1546 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F106" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Functional Efficiency</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Electricity reliability and security</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H107" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Functional Efficiency</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Electricity affordability</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Habitat of aquatic animals</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Birds</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
+        <v>3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Noise</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sense of Place</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Personal identity / connection to place</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sense of Place</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Ocean / landscape view</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>5</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Community benefits</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Job opportunities</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Tax revenues</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Indirect economic effects</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>4</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Recreational fishing</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-01-14 23:42:38</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Jia Mi</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Recreational boating</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Functional Efficiency</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Electricity reliability and security</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Functional Efficiency</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Electricity affordability</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Habitat of aquatic animals</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Birds</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Noise</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Sense of Place</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Personal identity / connection to place</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Sense of Place</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Ocean / landscape view</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Community benefits</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Job opportunities</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tax revenues</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Indirect economic effects</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Recreational fishing</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>5</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-01-19 15:14:21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Lenaig Hemery</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Recreational boating</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H136" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Functional Efficiency</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Electricity reliability and security</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" t="n">
+        <v>5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Functional Efficiency</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Electricity affordability</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Habitat of aquatic animals</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Birds</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>3</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Environmental Sustainability</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Noise</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sense of Place</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Personal identity / connection to place</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>5</v>
+      </c>
+      <c r="F143" t="n">
+        <v>5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Sense of Place</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Ocean / landscape view</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>5</v>
+      </c>
+      <c r="F144" t="n">
+        <v>5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Community benefits</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>7</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Job opportunities</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" t="n">
+        <v>5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tax revenues</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F147" t="n">
+        <v>5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Indirect economic effects</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>3</v>
+      </c>
+      <c r="F148" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Community Prosperity</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Tourism</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>3</v>
+      </c>
+      <c r="F149" t="n">
+        <v>5</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Recreational fishing</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3</v>
+      </c>
+      <c r="G150" t="n">
+        <v>3</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-01-20 11:44:51</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Michael Remige</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Recreational boating</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>4</v>
+      </c>
+      <c r="F151" t="n">
+        <v>3</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7152,239 +8709,239 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization - Recreational boating</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Aquatic Space Utilization - Recreational fishing</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Community Prosperity - Community benefits</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Community Prosperity - Indirect economic effects</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Community Prosperity - Job opportunities</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Community Prosperity - Tax revenues</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Community Prosperity - Tourism</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Environmental Sustainability - Birds</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Environmental Sustainability - Habitat of aquatic animals</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Environmental Sustainability - Health</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Environmental Sustainability - Noise</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Functional Efficiency - Electricity affordability</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Functional Efficiency - Electricity reliability and security</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Aquatic Space Utilization - Recreational boating</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Aquatic Space Utilization - Recreational fishing</t>
-        </is>
-      </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Sense of Place - Ocean / landscape view</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Sense of Place - Personal identity / connection to place</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Point Absorber</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3268073908151735</v>
+        <v>0.2523824664372489</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3731842024093764</v>
+        <v>0.4696579941537302</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2630893655427024</v>
+        <v>0.3064387569271468</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4050420168067227</v>
       </c>
       <c r="F2" t="n">
-        <v>0.351311563215734</v>
+        <v>0.2818198105726998</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2842170780538263</v>
+        <v>0.3175462820089731</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3500084906917815</v>
+        <v>0.3760747141145712</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3378346534692429</v>
+        <v>0.3208959728319489</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4613013055024499</v>
+        <v>0.3754816131159064</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3462984236653858</v>
+        <v>0.3133825939763987</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2374766570035555</v>
+        <v>0.3517311865726588</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2211558870408934</v>
+        <v>0.2903935838363282</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4528727682724318</v>
+        <v>0.2652277001681121</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2489642420643835</v>
+        <v>0.2665238672049784</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3483188533069919</v>
+        <v>0.353738020146012</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Oscillating Water Column</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3134547333809345</v>
+        <v>0.550787586542489</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3539407743546166</v>
+        <v>0.2610123574291268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4995552504682171</v>
+        <v>0.3690571260876186</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2840336134453782</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2803242040527506</v>
+        <v>0.4058935424323788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2007238919066411</v>
+        <v>0.3511597273871245</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3587995990356166</v>
+        <v>0.2940704010947918</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4010236734819326</v>
+        <v>0.2865113525900792</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08511180477239944</v>
+        <v>0.3390747802121842</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1751051375539961</v>
+        <v>0.4162978849809142</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4334023846332276</v>
+        <v>0.2653176381996623</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5754178501587025</v>
+        <v>0.2943819720309128</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2721200199021801</v>
+        <v>0.4323843440498769</v>
       </c>
       <c r="O3" t="n">
-        <v>0.089131187867961</v>
+        <v>0.1727267791526402</v>
       </c>
       <c r="P3" t="n">
-        <v>0.187013416796607</v>
+        <v>0.2220395325943402</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Oscillating Wave Surge Flap</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3597378758038919</v>
+        <v>0.1968299470202622</v>
       </c>
       <c r="C4" t="n">
-        <v>0.272875023236007</v>
+        <v>0.269329648417143</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2373553839890807</v>
+        <v>0.3245041169852347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3109243697478992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3683642327315155</v>
+        <v>0.3122866469949216</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5150590300395325</v>
+        <v>0.3312939906039025</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2911919102726018</v>
+        <v>0.3298548847906373</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2611416730488243</v>
+        <v>0.392592674577972</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4535868897251505</v>
+        <v>0.2854436066719095</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4785964387806183</v>
+        <v>0.2703195210426871</v>
       </c>
       <c r="L4" t="n">
-        <v>0.329120958363217</v>
+        <v>0.3829511752276791</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2034262628004043</v>
+        <v>0.4152244441327588</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2750072118253882</v>
+        <v>0.3023879557820108</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6619045700676556</v>
+        <v>0.5607493536423814</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4646677298964011</v>
+        <v>0.4242224472596479</v>
       </c>
     </row>
   </sheetData>
@@ -7402,107 +8959,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Aquatic Space Utilization</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Community Prosperity</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Environmental Sustainability</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Functional Efficiency</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Sense of Place</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Total Score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Point Absorber</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2086221890240418</v>
+        <v>0.2219315297454326</v>
       </c>
       <c r="C2" t="n">
-        <v>0.20399855236885</v>
+        <v>0.2074017218364815</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2218236696748613</v>
+        <v>0.209238871083864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1806873257787938</v>
+        <v>0.1707797391538137</v>
       </c>
       <c r="F2" t="n">
-        <v>0.184868263153453</v>
+        <v>0.1906481381804081</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Oscillating Water Column</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2856295270284697</v>
+        <v>0.2483617403092285</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2400337840978194</v>
+        <v>0.208554661764576</v>
       </c>
       <c r="D3" t="n">
-        <v>0.176199251594058</v>
+        <v>0.1999623679614069</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2050736868467214</v>
+        <v>0.222346587235368</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09306375043293148</v>
+        <v>0.1207746427294205</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Oscillating Wave Surge Flap</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.125841312030266</v>
+        <v>0.1340331369318599</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1653567344365474</v>
+        <v>0.1850362769747389</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2000299585947696</v>
+        <v>0.1913928750612538</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2124521430816539</v>
+        <v>0.2063324277847934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2963198518567632</v>
+        <v>0.2832052832473541</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -7559,32 +9116,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>WEC Design</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>PIS_sq</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>PIS_pct</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>NIS_sq</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>NIS_pct</t>
         </is>
@@ -7602,16 +9159,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0007310476447187828</v>
+        <v>0.0001961829708686795</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08132134349255424</v>
+        <v>0.04221673706136624</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009290025229905528</v>
+        <v>0.00159432273510262</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2110246802401013</v>
+        <v>0.5469873359335096</v>
       </c>
     </row>
     <row r="3">
@@ -7626,16 +9183,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.474301969634494e-05</v>
+        <v>1.268419120246015e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008314372971867462</v>
+        <v>0.0002729519093626108</v>
       </c>
       <c r="E3" t="n">
-        <v>2.448770941842486e-05</v>
+        <v>2.584405781230426e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005562429511171707</v>
+        <v>0.008866694315535814</v>
       </c>
     </row>
     <row r="4">
@@ -7650,16 +9207,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.926694603582828e-05</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006592822931791652</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001160442045944265</v>
+        <v>2.329370209889601e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2635966056305831</v>
+        <v>0.007991706932714485</v>
       </c>
     </row>
     <row r="5">
@@ -7674,10 +9231,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.001908216715349371</v>
+        <v>0.001124081728439953</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2122689924359903</v>
+        <v>0.2418918551131583</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -7698,16 +9255,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.006216341601852383</v>
+        <v>0.003325509370513552</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6915024681677963</v>
+        <v>0.7156184559161129</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002288408348030103</v>
+        <v>0.001271273778279158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5198162846181439</v>
+        <v>0.4361542628182402</v>
       </c>
     </row>
     <row r="7">
@@ -7728,10 +9285,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003308255381109718</v>
+        <v>0.002909038621349136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9408275988569278</v>
+        <v>0.714455929473286</v>
       </c>
     </row>
     <row r="8">
@@ -7752,10 +9309,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001847943977453212</v>
+        <v>3.856343271342204e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05255327944320407</v>
+        <v>0.009471126632952926</v>
       </c>
     </row>
     <row r="9">
@@ -7770,10 +9327,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001744212018147474</v>
+        <v>2.329370209889601e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09036285804975018</v>
+        <v>0.002667527767895065</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -7794,16 +9351,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001510000492715518</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07822899897411927</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.327498152521623e-05</v>
+        <v>0.001124081728439953</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006619121699868038</v>
+        <v>0.2760729438937611</v>
       </c>
     </row>
     <row r="11">
@@ -7818,10 +9375,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01604809881252587</v>
+        <v>0.008709024806164272</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8314081429761305</v>
+        <v>0.997332472232105</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -7842,10 +9399,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003308255381109718</v>
+        <v>0.002909038621349136</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9470965461574689</v>
+        <v>0.9834416912996459</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -7866,10 +9423,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0001847943977453212</v>
+        <v>3.856343271342204e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05290345384253114</v>
+        <v>0.01303691439903238</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -7890,16 +9447,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>7.20059265140818e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.00243426228977892</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001744212018147474</v>
+        <v>4.592290182518173e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08853631021163225</v>
+        <v>0.0004724253407408593</v>
       </c>
     </row>
     <row r="15">
@@ -7914,16 +9471,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3.215756496863608e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.001087132011542934</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001908216715349371</v>
+        <v>0.001007051518331088</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0968611988126488</v>
+        <v>0.1035989969671916</v>
       </c>
     </row>
     <row r="16">
@@ -7944,10 +9501,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01604809881252587</v>
+        <v>0.008709024806164272</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8146024909757189</v>
+        <v>0.8959285776920676</v>
       </c>
     </row>
   </sheetData>

--- a/streamlit_wec_full_app_repo/bluechoice_data.xlsx
+++ b/streamlit_wec_full_app_repo/bluechoice_data.xlsx
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6444811743331381</v>
+        <v>0.644481174333138</v>
       </c>
     </row>
     <row r="3">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4419563242340971</v>
+        <v>0.4419563242340972</v>
       </c>
     </row>
     <row r="4">
@@ -9162,13 +9162,13 @@
         <v>0.0001961829708686795</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04221673706136624</v>
+        <v>0.04221673706136625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00159432273510262</v>
+        <v>0.001594322735102621</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5469873359335096</v>
+        <v>0.5469873359335098</v>
       </c>
     </row>
     <row r="3">
@@ -9192,7 +9192,7 @@
         <v>2.584405781230426e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008866694315535814</v>
+        <v>0.008866694315535811</v>
       </c>
     </row>
     <row r="4">
@@ -9216,7 +9216,7 @@
         <v>2.329370209889601e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007991706932714485</v>
+        <v>0.007991706932714482</v>
       </c>
     </row>
     <row r="5">
@@ -9231,10 +9231,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.001124081728439953</v>
+        <v>0.001124081728439952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2418918551131583</v>
+        <v>0.2418918551131582</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9258,13 +9258,13 @@
         <v>0.003325509370513552</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7156184559161129</v>
+        <v>0.7156184559161131</v>
       </c>
       <c r="E6" t="n">
         <v>0.001271273778279158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4361542628182402</v>
+        <v>0.43615426281824</v>
       </c>
     </row>
     <row r="7">
@@ -9285,10 +9285,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002909038621349136</v>
+        <v>0.002909038621349138</v>
       </c>
       <c r="F7" t="n">
-        <v>0.714455929473286</v>
+        <v>0.7144559294732862</v>
       </c>
     </row>
     <row r="8">
@@ -9312,7 +9312,7 @@
         <v>3.856343271342204e-05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009471126632952926</v>
+        <v>0.009471126632952924</v>
       </c>
     </row>
     <row r="9">
@@ -9357,10 +9357,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001124081728439953</v>
+        <v>0.001124081728439952</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2760729438937611</v>
+        <v>0.2760729438937609</v>
       </c>
     </row>
     <row r="11">
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.002909038621349136</v>
+        <v>0.002909038621349138</v>
       </c>
       <c r="D12" t="n">
         <v>0.9834416912996459</v>
@@ -9426,7 +9426,7 @@
         <v>3.856343271342204e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01303691439903238</v>
+        <v>0.01303691439903237</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -9450,7 +9450,7 @@
         <v>7.20059265140818e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00243426228977892</v>
+        <v>0.002434262289778919</v>
       </c>
       <c r="E14" t="n">
         <v>4.592290182518173e-06</v>
@@ -9480,7 +9480,7 @@
         <v>0.001007051518331088</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1035989969671916</v>
+        <v>0.1035989969671915</v>
       </c>
     </row>
     <row r="16">

--- a/streamlit_wec_full_app_repo/bluechoice_data.xlsx
+++ b/streamlit_wec_full_app_repo/bluechoice_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-8840" yWindow="-28200" windowWidth="51200" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Themes Tab" sheetId="1" state="visible" r:id="rId1"/>
@@ -3502,11 +3502,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oscillating Wave Surge Flap</t>
+          <t>Point Absorber</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.644481174333138</v>
+        <v>0.6002671366060516</v>
       </c>
     </row>
     <row r="3">
@@ -3515,11 +3515,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Point Absorber</t>
+          <t>Oscillating Wave Surge Flap</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4419563242340972</v>
+        <v>0.5862739306747351</v>
       </c>
     </row>
     <row r="4">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4057682653851535</v>
+        <v>0.4755649691442913</v>
       </c>
     </row>
   </sheetData>
@@ -3863,10 +3863,10 @@
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="10">
@@ -4373,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H24" t="n">
         <v>0.2</v>
@@ -4883,10 +4883,10 @@
         <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
@@ -5393,10 +5393,10 @@
         <v>3</v>
       </c>
       <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
         <v>0.3333333333333333</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="55">
@@ -5903,10 +5903,10 @@
         <v>3</v>
       </c>
       <c r="G69" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H69" t="n">
         <v>0.2</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="70">
@@ -6416,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="85">
@@ -6920,10 +6920,10 @@
         <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
         <v>3</v>
@@ -7943,10 +7943,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G129" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -8453,10 +8453,10 @@
         <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="145">
@@ -8834,7 +8834,7 @@
         <v>0.2652277001681121</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2665238672049784</v>
+        <v>0.3688984991748724</v>
       </c>
       <c r="P2" t="n">
         <v>0.353738020146012</v>
@@ -8886,7 +8886,7 @@
         <v>0.4323843440498769</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1727267791526402</v>
+        <v>0.2005583434815231</v>
       </c>
       <c r="P3" t="n">
         <v>0.2220395325943402</v>
@@ -8938,7 +8938,7 @@
         <v>0.3023879557820108</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5607493536423814</v>
+        <v>0.4305431573436046</v>
       </c>
       <c r="P4" t="n">
         <v>0.4242224472596479</v>
@@ -8997,19 +8997,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2219315297454326</v>
+        <v>0.2151611401175667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2074017218364815</v>
+        <v>0.201074588112247</v>
       </c>
       <c r="D2" t="n">
-        <v>0.209238871083864</v>
+        <v>0.2028556920729432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1707797391538137</v>
+        <v>0.1655698197883999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1906481381804081</v>
+        <v>0.2153387599088432</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -9022,19 +9022,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2483617403092285</v>
+        <v>0.2462648499498761</v>
       </c>
       <c r="C3" t="n">
-        <v>0.208554661764576</v>
+        <v>0.2067938581113739</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1999623679614069</v>
+        <v>0.1982741080825323</v>
       </c>
       <c r="E3" t="n">
-        <v>0.222346587235368</v>
+        <v>0.2204693398999763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1207746427294205</v>
+        <v>0.1281978439562415</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -9047,19 +9047,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1340331369318599</v>
+        <v>0.1392461947502046</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1850362769747389</v>
+        <v>0.1922330406440914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1913928750612538</v>
+        <v>0.198836870975643</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2063324277847934</v>
+        <v>0.2143574796522908</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2832052832473541</v>
+        <v>0.2553264139777703</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -9162,13 +9162,13 @@
         <v>0.0001961829708686795</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04221673706136625</v>
+        <v>0.1100794258651354</v>
       </c>
       <c r="E2" t="n">
         <v>0.001594322735102621</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5469873359335098</v>
+        <v>0.3967086431318405</v>
       </c>
     </row>
     <row r="3">
@@ -9186,13 +9186,13 @@
         <v>1.268419120246015e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002729519093626108</v>
+        <v>0.0007117174742271824</v>
       </c>
       <c r="E3" t="n">
         <v>2.584405781230426e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008866694315535811</v>
+        <v>0.006430668572934916</v>
       </c>
     </row>
     <row r="4">
@@ -9216,7 +9216,7 @@
         <v>2.329370209889601e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007991706932714482</v>
+        <v>0.00579607425128736</v>
       </c>
     </row>
     <row r="5">
@@ -9234,7 +9234,7 @@
         <v>0.001124081728439952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2418918551131582</v>
+        <v>0.6307289095697637</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9255,16 +9255,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.003325509370513552</v>
+        <v>0.000460661595313857</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7156184559161131</v>
+        <v>0.2584799470908738</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001271273778279158</v>
+        <v>0.002375415228278072</v>
       </c>
       <c r="F6" t="n">
-        <v>0.43615426281824</v>
+        <v>0.5910646140439372</v>
       </c>
     </row>
     <row r="7">
@@ -9330,7 +9330,7 @@
         <v>2.329370209889601e-05</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002667527767895065</v>
+        <v>0.004704362723612285</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.008709024806164272</v>
+        <v>0.004928216941835835</v>
       </c>
       <c r="D11" t="n">
-        <v>0.997332472232105</v>
+        <v>0.9952956372763877</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
         <v>4.592290182518173e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004724253407408593</v>
+        <v>0.0007731309496183072</v>
       </c>
     </row>
     <row r="15">
@@ -9480,7 +9480,7 @@
         <v>0.001007051518331088</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1035989969671915</v>
+        <v>0.1695412671537532</v>
       </c>
     </row>
     <row r="16">
@@ -9501,10 +9501,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008709024806164272</v>
+        <v>0.004928216941835835</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8959285776920676</v>
+        <v>0.8296856018966285</v>
       </c>
     </row>
   </sheetData>
